--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29227,7 +29227,7 @@
         <v>169.58</v>
       </c>
       <c r="I686" t="n">
-        <v>192.98</v>
+        <v>193.42</v>
       </c>
       <c r="J686" t="n">
         <v>703</v>
@@ -29236,6 +29236,90 @@
         <v>550.25</v>
       </c>
       <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:56+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>644.24</v>
+      </c>
+      <c r="C687" t="n">
+        <v>658.64</v>
+      </c>
+      <c r="D687" t="n">
+        <v>189.22</v>
+      </c>
+      <c r="E687" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="F687" t="n">
+        <v>187.39</v>
+      </c>
+      <c r="G687" t="n">
+        <v>214.78</v>
+      </c>
+      <c r="H687" t="n">
+        <v>170.42</v>
+      </c>
+      <c r="I687" t="n">
+        <v>194.01</v>
+      </c>
+      <c r="J687" t="n">
+        <v>695.17</v>
+      </c>
+      <c r="K687" t="n">
+        <v>561.5700000000001</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>645.1799999999999</v>
+      </c>
+      <c r="C688" t="n">
+        <v>659.74</v>
+      </c>
+      <c r="D688" t="n">
+        <v>191.76</v>
+      </c>
+      <c r="E688" t="n">
+        <v>188.94</v>
+      </c>
+      <c r="F688" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="G688" t="n">
+        <v>215.96</v>
+      </c>
+      <c r="H688" t="n">
+        <v>171.91</v>
+      </c>
+      <c r="I688" t="n">
+        <v>196.73</v>
+      </c>
+      <c r="J688" t="n">
+        <v>686.3200000000001</v>
+      </c>
+      <c r="K688" t="n">
+        <v>549.79</v>
+      </c>
+      <c r="L688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29252,7 +29336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B733"/>
+  <dimension ref="A1:B735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36585,6 +36669,26 @@
       </c>
       <c r="B733" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -36747,28 +36851,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04284784840295064</v>
+        <v>-0.0431686857362667</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003472358561072308</v>
+        <v>0.003546511387237161</v>
       </c>
       <c r="M2" t="n">
-        <v>4.610441223651374</v>
+        <v>4.59857804986473</v>
       </c>
       <c r="N2" t="n">
-        <v>29.66732569173249</v>
+        <v>29.58251505702777</v>
       </c>
       <c r="O2" t="n">
-        <v>5.446772043305327</v>
+        <v>5.438981067904885</v>
       </c>
       <c r="P2" t="n">
-        <v>646.4002667659155</v>
+        <v>646.4035015823152</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36819,28 +36923,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1391916456552216</v>
+        <v>-0.1381083430392501</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02106995777410148</v>
+        <v>0.02087464041536724</v>
       </c>
       <c r="M3" t="n">
-        <v>4.671162684656601</v>
+        <v>4.662858818479894</v>
       </c>
       <c r="N3" t="n">
-        <v>50.68388623800944</v>
+        <v>50.54764105284929</v>
       </c>
       <c r="O3" t="n">
-        <v>7.119261635732278</v>
+        <v>7.109686424368467</v>
       </c>
       <c r="P3" t="n">
-        <v>660.9411744941518</v>
+        <v>660.9302460272664</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36891,28 +36995,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5646346726973401</v>
+        <v>-0.5659132785510953</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05310638817105284</v>
+        <v>0.05365322242964177</v>
       </c>
       <c r="M4" t="n">
-        <v>15.04380406763631</v>
+        <v>15.0064301022937</v>
       </c>
       <c r="N4" t="n">
-        <v>317.4953612075391</v>
+        <v>316.5861623664931</v>
       </c>
       <c r="O4" t="n">
-        <v>17.81839951307466</v>
+        <v>17.79286830071231</v>
       </c>
       <c r="P4" t="n">
-        <v>207.5386088399982</v>
+        <v>207.5515892566061</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36963,28 +37067,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3290949310227125</v>
+        <v>-0.3300084838187713</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03855479559880326</v>
+        <v>0.03899417721779719</v>
       </c>
       <c r="M5" t="n">
-        <v>10.84712269991069</v>
+        <v>10.82013597076193</v>
       </c>
       <c r="N5" t="n">
-        <v>152.0701924373519</v>
+        <v>151.6415569589743</v>
       </c>
       <c r="O5" t="n">
-        <v>12.3316743566051</v>
+        <v>12.31428264085953</v>
       </c>
       <c r="P5" t="n">
-        <v>197.679422183085</v>
+        <v>197.6886325018365</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37035,28 +37139,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2108296958917801</v>
+        <v>0.203723717791578</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01497323626279878</v>
+        <v>0.01404408461536821</v>
       </c>
       <c r="M6" t="n">
-        <v>10.5588588381887</v>
+        <v>10.56906439030526</v>
       </c>
       <c r="N6" t="n">
-        <v>164.7691690650581</v>
+        <v>164.7440638017791</v>
       </c>
       <c r="O6" t="n">
-        <v>12.8362443520314</v>
+        <v>12.83526640945871</v>
       </c>
       <c r="P6" t="n">
-        <v>195.7430623809047</v>
+        <v>195.8147362385003</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37107,28 +37211,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02992464026015495</v>
+        <v>-0.03053027564624849</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00104159698899009</v>
+        <v>0.001090922545365247</v>
       </c>
       <c r="M7" t="n">
-        <v>5.960526465832165</v>
+        <v>5.946103141016176</v>
       </c>
       <c r="N7" t="n">
-        <v>48.393340169953</v>
+        <v>48.25652251526773</v>
       </c>
       <c r="O7" t="n">
-        <v>6.956532194272732</v>
+        <v>6.946691479781417</v>
       </c>
       <c r="P7" t="n">
-        <v>217.2184822163267</v>
+        <v>217.224589559729</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37179,28 +37283,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1227063452405119</v>
+        <v>0.1173492003167469</v>
       </c>
       <c r="J8" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K8" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004370520478453876</v>
+        <v>0.004018770287904094</v>
       </c>
       <c r="M8" t="n">
-        <v>11.34587033845384</v>
+        <v>11.34128038166141</v>
       </c>
       <c r="N8" t="n">
-        <v>192.2594993668775</v>
+        <v>191.9540157294009</v>
       </c>
       <c r="O8" t="n">
-        <v>13.86576717556146</v>
+        <v>13.85474704674903</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3113093432019</v>
+        <v>177.3655301687118</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37251,28 +37355,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.204063795328602</v>
+        <v>-0.2080460826269358</v>
       </c>
       <c r="J9" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K9" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04074764252529417</v>
+        <v>0.04243778085342531</v>
       </c>
       <c r="M9" t="n">
-        <v>5.793930061881589</v>
+        <v>5.799210260988637</v>
       </c>
       <c r="N9" t="n">
-        <v>54.94794876279492</v>
+        <v>54.93035229818937</v>
       </c>
       <c r="O9" t="n">
-        <v>7.412688362719353</v>
+        <v>7.411501352505399</v>
       </c>
       <c r="P9" t="n">
-        <v>207.9073189117838</v>
+        <v>207.9476240311288</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37323,28 +37427,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.609341292258973</v>
+        <v>2.610525504782563</v>
       </c>
       <c r="J10" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K10" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1352775735519876</v>
+        <v>0.1361258618593844</v>
       </c>
       <c r="M10" t="n">
-        <v>29.1678912153377</v>
+        <v>29.09731273236947</v>
       </c>
       <c r="N10" t="n">
-        <v>2431.964138641552</v>
+        <v>2424.913169109105</v>
       </c>
       <c r="O10" t="n">
-        <v>49.31494842987826</v>
+        <v>49.24340736696746</v>
       </c>
       <c r="P10" t="n">
-        <v>620.1709699470349</v>
+        <v>620.1589540358893</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37395,28 +37499,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5661057692202344</v>
+        <v>0.4862887994207268</v>
       </c>
       <c r="J11" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="K11" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001095882168610562</v>
+        <v>0.0008112115385522367</v>
       </c>
       <c r="M11" t="n">
-        <v>102.6242757860815</v>
+        <v>102.874182249729</v>
       </c>
       <c r="N11" t="n">
-        <v>16447.90851080047</v>
+        <v>16456.73718698799</v>
       </c>
       <c r="O11" t="n">
-        <v>128.2493996508384</v>
+        <v>128.2838149845412</v>
       </c>
       <c r="P11" t="n">
-        <v>680.9111588291967</v>
+        <v>681.7162605175815</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37454,7 +37558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79926,7 +80030,7 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>-43.6307713032334,172.69102207490937</t>
+          <t>-43.63077481229589,172.6910246067932</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
@@ -79940,6 +80044,130 @@
         </is>
       </c>
       <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:56+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-43.63038694013076,172.69585246472687</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-43.63035732004003,172.69486077729337</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-43.63037046047704,172.6938690931516</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-43.63054268827609,172.69286199373116</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-43.63025681381388,172.69177043796708</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-43.6307795176296,172.69102800181966</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-43.630409810361094,172.6958524666925</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-43.630384422162194,172.69486077917713</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-43.630395941873026,172.69386909450373</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-43.63055324086113,172.69286029176982</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-43.630268696042386,172.69177901370358</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-43.63080121001413,172.69104365347403</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29320,6 +29320,90 @@
         <v>549.79</v>
       </c>
       <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:54+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>645.53</v>
+      </c>
+      <c r="C689" t="n">
+        <v>660.02</v>
+      </c>
+      <c r="D689" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="E689" t="n">
+        <v>189.81</v>
+      </c>
+      <c r="F689" t="n">
+        <v>191.38</v>
+      </c>
+      <c r="G689" t="n">
+        <v>216.55</v>
+      </c>
+      <c r="H689" t="n">
+        <v>172.69</v>
+      </c>
+      <c r="I689" t="n">
+        <v>197.28</v>
+      </c>
+      <c r="J689" t="n">
+        <v>684.71</v>
+      </c>
+      <c r="K689" t="n">
+        <v>561.49</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>647.08</v>
+      </c>
+      <c r="C690" t="n">
+        <v>660.99</v>
+      </c>
+      <c r="D690" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="E690" t="n">
+        <v>194.69</v>
+      </c>
+      <c r="F690" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="G690" t="n">
+        <v>219.13</v>
+      </c>
+      <c r="H690" t="n">
+        <v>176.67</v>
+      </c>
+      <c r="I690" t="n">
+        <v>197.64</v>
+      </c>
+      <c r="J690" t="n">
+        <v>670.95</v>
+      </c>
+      <c r="K690" t="n">
+        <v>612.5700000000001</v>
+      </c>
+      <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29336,7 +29420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B735"/>
+  <dimension ref="A1:B737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36689,6 +36773,26 @@
       </c>
       <c r="B735" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -36851,28 +36955,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0431686857362667</v>
+        <v>-0.04258201022112622</v>
       </c>
       <c r="J2" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K2" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003546511387237161</v>
+        <v>0.003472345329093351</v>
       </c>
       <c r="M2" t="n">
-        <v>4.59857804986473</v>
+        <v>4.58835105809167</v>
       </c>
       <c r="N2" t="n">
-        <v>29.58251505702777</v>
+        <v>29.5014585734129</v>
       </c>
       <c r="O2" t="n">
-        <v>5.438981067904885</v>
+        <v>5.431524516506659</v>
       </c>
       <c r="P2" t="n">
-        <v>646.4035015823152</v>
+        <v>646.3975654211681</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36923,28 +37027,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1381083430392501</v>
+        <v>-0.1362872636888227</v>
       </c>
       <c r="J3" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K3" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02087464041536724</v>
+        <v>0.0204531836980737</v>
       </c>
       <c r="M3" t="n">
-        <v>4.662858818479894</v>
+        <v>4.658153223550226</v>
       </c>
       <c r="N3" t="n">
-        <v>50.54764105284929</v>
+        <v>50.43122827202939</v>
       </c>
       <c r="O3" t="n">
-        <v>7.109686424368467</v>
+        <v>7.101494791382262</v>
       </c>
       <c r="P3" t="n">
-        <v>660.9302460272664</v>
+        <v>660.9118301337547</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36995,28 +37099,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5659132785510953</v>
+        <v>-0.5647887182421215</v>
       </c>
       <c r="J4" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K4" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05365322242964177</v>
+        <v>0.05376992848299667</v>
       </c>
       <c r="M4" t="n">
-        <v>15.0064301022937</v>
+        <v>14.96826535882814</v>
       </c>
       <c r="N4" t="n">
-        <v>316.5861623664931</v>
+        <v>315.6846979670559</v>
       </c>
       <c r="O4" t="n">
-        <v>17.79286830071231</v>
+        <v>17.76751805872323</v>
       </c>
       <c r="P4" t="n">
-        <v>207.5515892566061</v>
+        <v>207.5401315516466</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37067,28 +37171,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3300084838187713</v>
+        <v>-0.3281659508181184</v>
       </c>
       <c r="J5" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03899417721779719</v>
+        <v>0.03880010914112253</v>
       </c>
       <c r="M5" t="n">
-        <v>10.82013597076193</v>
+        <v>10.79823313407247</v>
       </c>
       <c r="N5" t="n">
-        <v>151.6415569589743</v>
+        <v>151.2490047139522</v>
       </c>
       <c r="O5" t="n">
-        <v>12.31428264085953</v>
+        <v>12.29833341205028</v>
       </c>
       <c r="P5" t="n">
-        <v>197.6886325018365</v>
+        <v>197.669989139967</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37139,28 +37243,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.203723717791578</v>
+        <v>0.2005772492925079</v>
       </c>
       <c r="J6" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K6" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01404408461536821</v>
+        <v>0.01369301889077479</v>
       </c>
       <c r="M6" t="n">
-        <v>10.56906439030526</v>
+        <v>10.55636965686984</v>
       </c>
       <c r="N6" t="n">
-        <v>164.7440638017791</v>
+        <v>164.4061479876556</v>
       </c>
       <c r="O6" t="n">
-        <v>12.83526640945871</v>
+        <v>12.82209608401277</v>
       </c>
       <c r="P6" t="n">
-        <v>195.8147362385003</v>
+        <v>195.8465292334643</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37211,28 +37315,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03053027564624849</v>
+        <v>-0.02972251342716772</v>
       </c>
       <c r="J7" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K7" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001090922545365247</v>
+        <v>0.001040334152689448</v>
       </c>
       <c r="M7" t="n">
-        <v>5.946103141016176</v>
+        <v>5.933107889727574</v>
       </c>
       <c r="N7" t="n">
-        <v>48.25652251526773</v>
+        <v>48.12690940996603</v>
       </c>
       <c r="O7" t="n">
-        <v>6.946691479781417</v>
+        <v>6.937356082108372</v>
       </c>
       <c r="P7" t="n">
-        <v>217.224589559729</v>
+        <v>217.2164148308871</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37283,28 +37387,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1173492003167469</v>
+        <v>0.1140634392633098</v>
       </c>
       <c r="J8" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K8" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004018770287904094</v>
+        <v>0.003819616393708314</v>
       </c>
       <c r="M8" t="n">
-        <v>11.34128038166141</v>
+        <v>11.325762252249</v>
       </c>
       <c r="N8" t="n">
-        <v>191.9540157294009</v>
+        <v>191.5034783380708</v>
       </c>
       <c r="O8" t="n">
-        <v>13.85474704674903</v>
+        <v>13.83847817999042</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3655301687118</v>
+        <v>177.3988573115064</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37355,28 +37459,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2080460826269358</v>
+        <v>-0.2109019891318333</v>
       </c>
       <c r="J9" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K9" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04243778085342531</v>
+        <v>0.04376900681105433</v>
       </c>
       <c r="M9" t="n">
-        <v>5.799210260988637</v>
+        <v>5.79822295409885</v>
       </c>
       <c r="N9" t="n">
-        <v>54.93035229818937</v>
+        <v>54.84322443100449</v>
       </c>
       <c r="O9" t="n">
-        <v>7.411501352505399</v>
+        <v>7.405621137420175</v>
       </c>
       <c r="P9" t="n">
-        <v>207.9476240311288</v>
+        <v>207.9765995126481</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37427,28 +37531,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.610525504782563</v>
+        <v>2.604226278061521</v>
       </c>
       <c r="J10" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K10" t="n">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1361258618593844</v>
+        <v>0.1362792164827236</v>
       </c>
       <c r="M10" t="n">
-        <v>29.09731273236947</v>
+        <v>29.03465548845173</v>
       </c>
       <c r="N10" t="n">
-        <v>2424.913169109105</v>
+        <v>2418.323838713206</v>
       </c>
       <c r="O10" t="n">
-        <v>49.24340736696746</v>
+        <v>49.17645614227612</v>
       </c>
       <c r="P10" t="n">
-        <v>620.1589540358893</v>
+        <v>620.2231327153904</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37499,28 +37603,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4862887994207268</v>
+        <v>0.4253534501554711</v>
       </c>
       <c r="J11" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K11" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0008112115385522367</v>
+        <v>0.0006233675053742838</v>
       </c>
       <c r="M11" t="n">
-        <v>102.874182249729</v>
+        <v>102.9913770862718</v>
       </c>
       <c r="N11" t="n">
-        <v>16456.73718698799</v>
+        <v>16444.08350257771</v>
       </c>
       <c r="O11" t="n">
-        <v>128.2838149845412</v>
+        <v>128.2344864011928</v>
       </c>
       <c r="P11" t="n">
-        <v>681.7162605175815</v>
+        <v>682.33225208147</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37558,7 +37662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80173,6 +80277,130 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:54+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-43.630418724348466,172.6958524674586</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-43.63039225566593,172.6948607797216</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-43.63040638654415,172.69386909505792</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-43.630558517153624,172.69285944078894</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-43.63027491626912,172.69178350301667</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-43.63080559634162,172.69104681833196</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-43.630452489452075,172.69585247036045</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-43.630436195318815,172.6948607827755</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-43.630482740690994,172.6938690991091</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-43.63058158975461,172.69285571954862</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-43.63030665537197,172.6918064100388</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-43.630808467392285,172.6910488898756</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29404,6 +29404,90 @@
         <v>612.5700000000001</v>
       </c>
       <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>647.3099999999999</v>
+      </c>
+      <c r="C691" t="n">
+        <v>661.21</v>
+      </c>
+      <c r="D691" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="E691" t="n">
+        <v>195.47</v>
+      </c>
+      <c r="F691" t="n">
+        <v>200.46</v>
+      </c>
+      <c r="G691" t="n">
+        <v>219.35</v>
+      </c>
+      <c r="H691" t="n">
+        <v>177.27</v>
+      </c>
+      <c r="I691" t="n">
+        <v>198.23</v>
+      </c>
+      <c r="J691" t="n">
+        <v>670.0700000000001</v>
+      </c>
+      <c r="K691" t="n">
+        <v>620.9400000000001</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>648.39</v>
+      </c>
+      <c r="C692" t="n">
+        <v>662.1</v>
+      </c>
+      <c r="D692" t="n">
+        <v>201.22</v>
+      </c>
+      <c r="E692" t="n">
+        <v>197.35</v>
+      </c>
+      <c r="F692" t="n">
+        <v>204.22</v>
+      </c>
+      <c r="G692" t="n">
+        <v>221.7</v>
+      </c>
+      <c r="H692" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="I692" t="n">
+        <v>199.41</v>
+      </c>
+      <c r="J692" t="n">
+        <v>669.48</v>
+      </c>
+      <c r="K692" t="n">
+        <v>674.6799999999999</v>
+      </c>
+      <c r="L692" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29420,7 +29504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B737"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36793,6 +36877,26 @@
       </c>
       <c r="B737" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -36955,28 +37059,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04258201022112622</v>
+        <v>-0.04113134258692924</v>
       </c>
       <c r="J2" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003472345329093351</v>
+        <v>0.003258751729693476</v>
       </c>
       <c r="M2" t="n">
-        <v>4.58835105809167</v>
+        <v>4.582756352439197</v>
       </c>
       <c r="N2" t="n">
-        <v>29.5014585734129</v>
+        <v>29.43585825692913</v>
       </c>
       <c r="O2" t="n">
-        <v>5.431524516506659</v>
+        <v>5.425482306387988</v>
       </c>
       <c r="P2" t="n">
-        <v>646.3975654211681</v>
+        <v>646.3828653063968</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37027,28 +37131,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1362872636888227</v>
+        <v>-0.1338405968574523</v>
       </c>
       <c r="J3" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K3" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0204531836980737</v>
+        <v>0.01984088223926028</v>
       </c>
       <c r="M3" t="n">
-        <v>4.658153223550226</v>
+        <v>4.656450271304228</v>
       </c>
       <c r="N3" t="n">
-        <v>50.43122827202939</v>
+        <v>50.33975635293866</v>
       </c>
       <c r="O3" t="n">
-        <v>7.101494791382262</v>
+        <v>7.095051539836668</v>
       </c>
       <c r="P3" t="n">
-        <v>660.9118301337547</v>
+        <v>660.8870396801545</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37099,28 +37203,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5647887182421215</v>
+        <v>-0.5610659470791726</v>
       </c>
       <c r="J4" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K4" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05376992848299667</v>
+        <v>0.05339767641157434</v>
       </c>
       <c r="M4" t="n">
-        <v>14.96826535882814</v>
+        <v>14.94316789391495</v>
       </c>
       <c r="N4" t="n">
-        <v>315.6846979670559</v>
+        <v>314.9023217953279</v>
       </c>
       <c r="O4" t="n">
-        <v>17.76751805872323</v>
+        <v>17.7454873642661</v>
       </c>
       <c r="P4" t="n">
-        <v>207.5401315516466</v>
+        <v>207.5021495036776</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37171,28 +37275,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3281659508181184</v>
+        <v>-0.3239984355331601</v>
       </c>
       <c r="J5" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K5" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03880010914112253</v>
+        <v>0.03804933834338531</v>
       </c>
       <c r="M5" t="n">
-        <v>10.79823313407247</v>
+        <v>10.78844431915397</v>
       </c>
       <c r="N5" t="n">
-        <v>151.2490047139522</v>
+        <v>150.9702207537573</v>
       </c>
       <c r="O5" t="n">
-        <v>12.29833341205028</v>
+        <v>12.28699396735252</v>
       </c>
       <c r="P5" t="n">
-        <v>197.669989139967</v>
+        <v>197.6277615090083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37243,28 +37347,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2005772492925079</v>
+        <v>0.2012607840759081</v>
       </c>
       <c r="J6" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01369301889077479</v>
+        <v>0.01386980589158726</v>
       </c>
       <c r="M6" t="n">
-        <v>10.55636965686984</v>
+        <v>10.53079539241947</v>
       </c>
       <c r="N6" t="n">
-        <v>164.4061479876556</v>
+        <v>163.9439546840333</v>
       </c>
       <c r="O6" t="n">
-        <v>12.82209608401277</v>
+        <v>12.80406008592717</v>
       </c>
       <c r="P6" t="n">
-        <v>195.8465292334643</v>
+        <v>195.8395937436411</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37315,28 +37419,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02972251342716772</v>
+        <v>-0.027411081172644</v>
       </c>
       <c r="J7" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K7" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001040334152689448</v>
+        <v>0.0008895694960893152</v>
       </c>
       <c r="M7" t="n">
-        <v>5.933107889727574</v>
+        <v>5.928117934040025</v>
       </c>
       <c r="N7" t="n">
-        <v>48.12690940996603</v>
+        <v>48.03957483466448</v>
       </c>
       <c r="O7" t="n">
-        <v>6.937356082108372</v>
+        <v>6.931058709509283</v>
       </c>
       <c r="P7" t="n">
-        <v>217.2164148308871</v>
+        <v>217.1929895409345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37387,28 +37491,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1140634392633098</v>
+        <v>0.1135592675140269</v>
       </c>
       <c r="J8" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K8" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003819616393708314</v>
+        <v>0.003809582164924108</v>
       </c>
       <c r="M8" t="n">
-        <v>11.325762252249</v>
+        <v>11.29953276324445</v>
       </c>
       <c r="N8" t="n">
-        <v>191.5034783380708</v>
+        <v>190.9652289866041</v>
       </c>
       <c r="O8" t="n">
-        <v>13.83847817999042</v>
+        <v>13.81901693271284</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3988573115064</v>
+        <v>177.403970833096</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37459,28 +37563,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2109019891318333</v>
+        <v>-0.2129412183971259</v>
       </c>
       <c r="J9" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K9" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04376900681105433</v>
+        <v>0.04482106348520776</v>
       </c>
       <c r="M9" t="n">
-        <v>5.79822295409885</v>
+        <v>5.792678939660322</v>
       </c>
       <c r="N9" t="n">
-        <v>54.84322443100449</v>
+        <v>54.72252986174756</v>
       </c>
       <c r="O9" t="n">
-        <v>7.405621137420175</v>
+        <v>7.397467800656354</v>
       </c>
       <c r="P9" t="n">
-        <v>207.9765995126481</v>
+        <v>207.9973277391762</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37531,28 +37635,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.604226278061521</v>
+        <v>2.593379034456794</v>
       </c>
       <c r="J10" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K10" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1362792164827236</v>
+        <v>0.1359885656493758</v>
       </c>
       <c r="M10" t="n">
-        <v>29.03465548845173</v>
+        <v>28.9883061125904</v>
       </c>
       <c r="N10" t="n">
-        <v>2418.323838713206</v>
+        <v>2412.332997646535</v>
       </c>
       <c r="O10" t="n">
-        <v>49.17645614227612</v>
+        <v>49.11550669235262</v>
       </c>
       <c r="P10" t="n">
-        <v>620.2231327153904</v>
+        <v>620.333804418106</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37603,28 +37707,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4253534501554711</v>
+        <v>0.3995802526415325</v>
       </c>
       <c r="J11" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K11" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006233675053742838</v>
+        <v>0.0005533532706862854</v>
       </c>
       <c r="M11" t="n">
-        <v>102.9913770862718</v>
+        <v>102.8680543001741</v>
       </c>
       <c r="N11" t="n">
-        <v>16444.08350257771</v>
+        <v>16404.57348558348</v>
       </c>
       <c r="O11" t="n">
-        <v>128.2344864011928</v>
+        <v>128.0803399651308</v>
       </c>
       <c r="P11" t="n">
-        <v>682.33225208147</v>
+        <v>682.5932253682406</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37662,7 +37766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80401,6 +80505,130 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-43.63045861219084,172.69585247088665</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-43.63044321846004,172.6948607832636</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-43.630488143107,172.69386909939573</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-43.6305835571857,172.69285540223342</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-43.63031144016094,172.69180986336082</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-43.63081317272524,172.69105228490582</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-43.63049498846219,172.69585247401278</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-43.630460146031105,172.69486078444004</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-43.63052199824723,172.69386910119178</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-43.63060457292669,172.69285201272885</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-43.630347166581835,172.69183564818238</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>-43.63082258339086,172.69105907496794</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L692"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29488,6 +29488,132 @@
         <v>674.6799999999999</v>
       </c>
       <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>650.58</v>
+      </c>
+      <c r="C693" t="n">
+        <v>661.37</v>
+      </c>
+      <c r="D693" t="n">
+        <v>206</v>
+      </c>
+      <c r="E693" t="n">
+        <v>202.92</v>
+      </c>
+      <c r="F693" t="n">
+        <v>210.52</v>
+      </c>
+      <c r="G693" t="n">
+        <v>224.79</v>
+      </c>
+      <c r="H693" t="n">
+        <v>182.94</v>
+      </c>
+      <c r="I693" t="n">
+        <v>200.12</v>
+      </c>
+      <c r="J693" t="n">
+        <v>660.58</v>
+      </c>
+      <c r="K693" t="n">
+        <v>730.54</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>650.7</v>
+      </c>
+      <c r="C694" t="n">
+        <v>661.6900000000001</v>
+      </c>
+      <c r="D694" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="E694" t="n">
+        <v>203.05</v>
+      </c>
+      <c r="F694" t="n">
+        <v>210.95</v>
+      </c>
+      <c r="G694" t="n">
+        <v>224.94</v>
+      </c>
+      <c r="H694" t="n">
+        <v>183.11</v>
+      </c>
+      <c r="I694" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="J694" t="n">
+        <v>660.91</v>
+      </c>
+      <c r="K694" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>650.16</v>
+      </c>
+      <c r="C695" t="n">
+        <v>661.49</v>
+      </c>
+      <c r="D695" t="n">
+        <v>205.99</v>
+      </c>
+      <c r="E695" t="n">
+        <v>203.63</v>
+      </c>
+      <c r="F695" t="n">
+        <v>211.63</v>
+      </c>
+      <c r="G695" t="n">
+        <v>224.96</v>
+      </c>
+      <c r="H695" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="I695" t="n">
+        <v>199.73</v>
+      </c>
+      <c r="J695" t="n">
+        <v>660.27</v>
+      </c>
+      <c r="K695" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="L695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29504,7 +29630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36897,6 +37023,36 @@
       </c>
       <c r="B739" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -37059,28 +37215,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04113134258692924</v>
+        <v>-0.03675767180608569</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003258751729693476</v>
+        <v>0.002618781202790799</v>
       </c>
       <c r="M2" t="n">
-        <v>4.582756352439197</v>
+        <v>4.586002782949562</v>
       </c>
       <c r="N2" t="n">
-        <v>29.43585825692913</v>
+        <v>29.42361890256067</v>
       </c>
       <c r="O2" t="n">
-        <v>5.425482306387988</v>
+        <v>5.424354238299769</v>
       </c>
       <c r="P2" t="n">
-        <v>646.3828653063968</v>
+        <v>646.3383350527209</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37131,28 +37287,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1338405968574523</v>
+        <v>-0.1303225758839492</v>
       </c>
       <c r="J3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01984088223926028</v>
+        <v>0.01897939597236709</v>
       </c>
       <c r="M3" t="n">
-        <v>4.656450271304228</v>
+        <v>4.653009566767574</v>
       </c>
       <c r="N3" t="n">
-        <v>50.33975635293866</v>
+        <v>50.19647001995887</v>
       </c>
       <c r="O3" t="n">
-        <v>7.095051539836668</v>
+        <v>7.084946719627387</v>
       </c>
       <c r="P3" t="n">
-        <v>660.8870396801545</v>
+        <v>660.8512197690461</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37203,28 +37359,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5610659470791726</v>
+        <v>-0.5497638156270247</v>
       </c>
       <c r="J4" t="n">
+        <v>694</v>
+      </c>
+      <c r="K4" t="n">
         <v>691</v>
       </c>
-      <c r="K4" t="n">
-        <v>688</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05339767641157434</v>
+        <v>0.05172482438051418</v>
       </c>
       <c r="M4" t="n">
-        <v>14.94316789391495</v>
+        <v>14.93427190729187</v>
       </c>
       <c r="N4" t="n">
-        <v>314.9023217953279</v>
+        <v>314.2928093383949</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7454873642661</v>
+        <v>17.72830531490235</v>
       </c>
       <c r="P4" t="n">
-        <v>207.5021495036776</v>
+        <v>207.3863015184806</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37275,28 +37431,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3239984355331601</v>
+        <v>-0.3120740641963858</v>
       </c>
       <c r="J5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03804933834338531</v>
+        <v>0.03552830458976897</v>
       </c>
       <c r="M5" t="n">
-        <v>10.78844431915397</v>
+        <v>10.80306797359997</v>
       </c>
       <c r="N5" t="n">
-        <v>150.9702207537573</v>
+        <v>151.1709984194515</v>
       </c>
       <c r="O5" t="n">
-        <v>12.28699396735252</v>
+        <v>12.29516158573979</v>
       </c>
       <c r="P5" t="n">
-        <v>197.6277615090083</v>
+        <v>197.5063487664862</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37347,28 +37503,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2012607840759081</v>
+        <v>0.2095787093217036</v>
       </c>
       <c r="J6" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K6" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01386980589158726</v>
+        <v>0.01512528527729951</v>
       </c>
       <c r="M6" t="n">
-        <v>10.53079539241947</v>
+        <v>10.52252312238144</v>
       </c>
       <c r="N6" t="n">
-        <v>163.9439546840333</v>
+        <v>163.6506986194676</v>
       </c>
       <c r="O6" t="n">
-        <v>12.80406008592717</v>
+        <v>12.79260327765493</v>
       </c>
       <c r="P6" t="n">
-        <v>195.8395937436411</v>
+        <v>195.7548950519195</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37419,28 +37575,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.027411081172644</v>
+        <v>-0.02030383929118368</v>
       </c>
       <c r="J7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008895694960893152</v>
+        <v>0.0004898104227183397</v>
       </c>
       <c r="M7" t="n">
-        <v>5.928117934040025</v>
+        <v>5.939764531430799</v>
       </c>
       <c r="N7" t="n">
-        <v>48.03957483466448</v>
+        <v>48.13507643463799</v>
       </c>
       <c r="O7" t="n">
-        <v>6.931058709509283</v>
+        <v>6.937944683740134</v>
       </c>
       <c r="P7" t="n">
-        <v>217.1929895409345</v>
+        <v>217.1206211546544</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37491,28 +37647,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1135592675140269</v>
+        <v>0.1155329624970454</v>
       </c>
       <c r="J8" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K8" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003809582164924108</v>
+        <v>0.003979633792591808</v>
       </c>
       <c r="M8" t="n">
-        <v>11.29953276324445</v>
+        <v>11.26016416692114</v>
       </c>
       <c r="N8" t="n">
-        <v>190.9652289866041</v>
+        <v>190.1624865129145</v>
       </c>
       <c r="O8" t="n">
-        <v>13.81901693271284</v>
+        <v>13.78994149780609</v>
       </c>
       <c r="P8" t="n">
-        <v>177.403970833096</v>
+        <v>177.3838085179786</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37563,28 +37719,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2129412183971259</v>
+        <v>-0.2147643485234504</v>
       </c>
       <c r="J9" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K9" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04482106348520776</v>
+        <v>0.04595521882642239</v>
       </c>
       <c r="M9" t="n">
-        <v>5.792678939660322</v>
+        <v>5.777650609680172</v>
       </c>
       <c r="N9" t="n">
-        <v>54.72252986174756</v>
+        <v>54.50623934398448</v>
       </c>
       <c r="O9" t="n">
-        <v>7.397467800656354</v>
+        <v>7.382834099719733</v>
       </c>
       <c r="P9" t="n">
-        <v>207.9973277391762</v>
+        <v>208.015955048193</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37635,28 +37791,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.593379034456794</v>
+        <v>2.56926790939989</v>
       </c>
       <c r="J10" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K10" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1359885656493758</v>
+        <v>0.1347471930710621</v>
       </c>
       <c r="M10" t="n">
-        <v>28.9883061125904</v>
+        <v>28.94579706640078</v>
       </c>
       <c r="N10" t="n">
-        <v>2412.332997646535</v>
+        <v>2405.296710082491</v>
       </c>
       <c r="O10" t="n">
-        <v>49.11550669235262</v>
+        <v>49.04382438271399</v>
       </c>
       <c r="P10" t="n">
-        <v>620.333804418106</v>
+        <v>620.5810195129316</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37707,28 +37863,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3995802526415325</v>
+        <v>0.4313893072737104</v>
       </c>
       <c r="J11" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K11" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005533532706862854</v>
+        <v>0.0006508025635518777</v>
       </c>
       <c r="M11" t="n">
-        <v>102.8680543001741</v>
+        <v>102.5327717994904</v>
       </c>
       <c r="N11" t="n">
-        <v>16404.57348558348</v>
+        <v>16339.73051695231</v>
       </c>
       <c r="O11" t="n">
-        <v>128.0803399651308</v>
+        <v>127.826955361349</v>
       </c>
       <c r="P11" t="n">
-        <v>682.5932253682406</v>
+        <v>682.269352926044</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37766,7 +37922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L692"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80629,6 +80785,192 @@
         </is>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-43.630538027713634,172.69585247771136</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-43.63051029846217,172.69486078792545</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-43.63057872361469,172.69386910420096</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-43.6306322063901,172.69284755588728</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-43.63035665641141,172.69184249728073</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>-43.63082824574031,172.6910631605148</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-43.63053694723035,172.6958524776185</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-43.6305114689857,172.6948607880068</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-43.63058259534612,172.6938691044063</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-43.63063354782036,172.69284733953563</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-43.63035801210131,172.69184347572354</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>-43.630833509332625,172.6910669583478</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-43.63053793767337,172.69585247770362</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-43.630516691321375,172.6948607883697</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-43.63058871808417,172.69386910473108</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-43.630633726677736,172.69284731068876</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-43.63035059567996,172.69183812306642</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>-43.6308251354357,172.6910609163411</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29614,6 +29614,132 @@
         <v>731.08</v>
       </c>
       <c r="L695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>650.8</v>
+      </c>
+      <c r="C696" t="n">
+        <v>661.77</v>
+      </c>
+      <c r="D696" t="n">
+        <v>209.15</v>
+      </c>
+      <c r="E696" t="n">
+        <v>205.69</v>
+      </c>
+      <c r="F696" t="n">
+        <v>212.51</v>
+      </c>
+      <c r="G696" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="H696" t="n">
+        <v>183.54</v>
+      </c>
+      <c r="I696" t="n">
+        <v>201.64</v>
+      </c>
+      <c r="J696" t="n">
+        <v>652.95</v>
+      </c>
+      <c r="K696" t="n">
+        <v>763.51</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>650.77</v>
+      </c>
+      <c r="C697" t="n">
+        <v>661.79</v>
+      </c>
+      <c r="D697" t="n">
+        <v>208.55</v>
+      </c>
+      <c r="E697" t="n">
+        <v>205.06</v>
+      </c>
+      <c r="F697" t="n">
+        <v>212.49</v>
+      </c>
+      <c r="G697" t="n">
+        <v>225.66</v>
+      </c>
+      <c r="H697" t="n">
+        <v>183.24</v>
+      </c>
+      <c r="I697" t="n">
+        <v>201.47</v>
+      </c>
+      <c r="J697" t="n">
+        <v>653.24</v>
+      </c>
+      <c r="K697" t="n">
+        <v>763.74</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>650.71</v>
+      </c>
+      <c r="C698" t="n">
+        <v>662.02</v>
+      </c>
+      <c r="D698" t="n">
+        <v>208.96</v>
+      </c>
+      <c r="E698" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="F698" t="n">
+        <v>212.74</v>
+      </c>
+      <c r="G698" t="n">
+        <v>225.91</v>
+      </c>
+      <c r="H698" t="n">
+        <v>183.46</v>
+      </c>
+      <c r="I698" t="n">
+        <v>202.09</v>
+      </c>
+      <c r="J698" t="n">
+        <v>653.16</v>
+      </c>
+      <c r="K698" t="n">
+        <v>763.77</v>
+      </c>
+      <c r="L698" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29630,7 +29756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37053,6 +37179,36 @@
       </c>
       <c r="B742" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -37215,28 +37371,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03675767180608569</v>
+        <v>-0.03224105334600086</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K2" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002618781202790799</v>
+        <v>0.002026508692181128</v>
       </c>
       <c r="M2" t="n">
-        <v>4.586002782949562</v>
+        <v>4.589937339799802</v>
       </c>
       <c r="N2" t="n">
-        <v>29.42361890256067</v>
+        <v>29.42064027210501</v>
       </c>
       <c r="O2" t="n">
-        <v>5.424354238299769</v>
+        <v>5.424079670516004</v>
       </c>
       <c r="P2" t="n">
-        <v>646.3383350527209</v>
+        <v>646.2921994848366</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37287,28 +37443,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1303225758839492</v>
+        <v>-0.1265838148656299</v>
       </c>
       <c r="J3" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K3" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01897939597236709</v>
+        <v>0.01806207140583116</v>
       </c>
       <c r="M3" t="n">
-        <v>4.653009566767574</v>
+        <v>4.650775600747123</v>
       </c>
       <c r="N3" t="n">
-        <v>50.19647001995887</v>
+        <v>50.06520299455828</v>
       </c>
       <c r="O3" t="n">
-        <v>7.084946719627387</v>
+        <v>7.075676857697664</v>
       </c>
       <c r="P3" t="n">
-        <v>660.8512197690461</v>
+        <v>660.8130291628701</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37359,28 +37515,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5497638156270247</v>
+        <v>-0.5361965233959086</v>
       </c>
       <c r="J4" t="n">
+        <v>697</v>
+      </c>
+      <c r="K4" t="n">
         <v>694</v>
       </c>
-      <c r="K4" t="n">
-        <v>691</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05172482438051418</v>
+        <v>0.0496074262642473</v>
       </c>
       <c r="M4" t="n">
-        <v>14.93427190729187</v>
+        <v>14.93742726316018</v>
       </c>
       <c r="N4" t="n">
-        <v>314.2928093383949</v>
+        <v>314.0376234369398</v>
       </c>
       <c r="O4" t="n">
-        <v>17.72830531490235</v>
+        <v>17.72110672156058</v>
       </c>
       <c r="P4" t="n">
-        <v>207.3863015184806</v>
+        <v>207.2467880191672</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37431,28 +37587,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3120740641963858</v>
+        <v>-0.2984939824728031</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03552830458976897</v>
+        <v>0.03266637839605813</v>
       </c>
       <c r="M5" t="n">
-        <v>10.80306797359997</v>
+        <v>10.8259318946732</v>
       </c>
       <c r="N5" t="n">
-        <v>151.1709984194515</v>
+        <v>151.6385405677398</v>
       </c>
       <c r="O5" t="n">
-        <v>12.29516158573979</v>
+        <v>12.31416016493775</v>
       </c>
       <c r="P5" t="n">
-        <v>197.5063487664862</v>
+        <v>197.3676325674301</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37503,28 +37659,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2095787093217036</v>
+        <v>0.2190073414500813</v>
       </c>
       <c r="J6" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K6" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01512528527729951</v>
+        <v>0.01659351417635802</v>
       </c>
       <c r="M6" t="n">
-        <v>10.52252312238144</v>
+        <v>10.5190392933298</v>
       </c>
       <c r="N6" t="n">
-        <v>163.6506986194676</v>
+        <v>163.4849589278122</v>
       </c>
       <c r="O6" t="n">
-        <v>12.79260327765493</v>
+        <v>12.78612368655224</v>
       </c>
       <c r="P6" t="n">
-        <v>195.7548950519195</v>
+        <v>195.6585784824971</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37575,28 +37731,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02030383929118368</v>
+        <v>-0.01257298090181849</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K7" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004898104227183397</v>
+        <v>0.0001882346328566653</v>
       </c>
       <c r="M7" t="n">
-        <v>5.939764531430799</v>
+        <v>5.954751943528786</v>
       </c>
       <c r="N7" t="n">
-        <v>48.13507643463799</v>
+        <v>48.29041991977452</v>
       </c>
       <c r="O7" t="n">
-        <v>6.937944683740134</v>
+        <v>6.949130875136438</v>
       </c>
       <c r="P7" t="n">
-        <v>217.1206211546544</v>
+        <v>217.0416480324473</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37647,28 +37803,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1155329624970454</v>
+        <v>0.1180208311949069</v>
       </c>
       <c r="J8" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K8" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003979633792591808</v>
+        <v>0.004190611618922313</v>
       </c>
       <c r="M8" t="n">
-        <v>11.26016416692114</v>
+        <v>11.22359497440162</v>
       </c>
       <c r="N8" t="n">
-        <v>190.1624865129145</v>
+        <v>189.3801635962178</v>
       </c>
       <c r="O8" t="n">
-        <v>13.78994149780609</v>
+        <v>13.76154655539187</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3838085179786</v>
+        <v>177.3583088618533</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37719,28 +37875,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2147643485234504</v>
+        <v>-0.21525705032425</v>
       </c>
       <c r="J9" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K9" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04595521882642239</v>
+        <v>0.04657320895587691</v>
       </c>
       <c r="M9" t="n">
-        <v>5.777650609680172</v>
+        <v>5.755444014201252</v>
       </c>
       <c r="N9" t="n">
-        <v>54.50623934398448</v>
+        <v>54.27305948668909</v>
       </c>
       <c r="O9" t="n">
-        <v>7.382834099719733</v>
+        <v>7.367025144974672</v>
       </c>
       <c r="P9" t="n">
-        <v>208.015955048193</v>
+        <v>208.0210041165188</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37791,28 +37947,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.56926790939989</v>
+        <v>2.539206624810384</v>
       </c>
       <c r="J10" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K10" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1347471930710621</v>
+        <v>0.1328536701527865</v>
       </c>
       <c r="M10" t="n">
-        <v>28.94579706640078</v>
+        <v>28.92341665401563</v>
       </c>
       <c r="N10" t="n">
-        <v>2405.296710082491</v>
+        <v>2400.305910898433</v>
       </c>
       <c r="O10" t="n">
-        <v>49.04382438271399</v>
+        <v>48.99291694621206</v>
       </c>
       <c r="P10" t="n">
-        <v>620.5810195129316</v>
+        <v>620.8902342170342</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37863,28 +38019,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4313893072737104</v>
+        <v>0.4899367842602421</v>
       </c>
       <c r="J11" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K11" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006508025635518777</v>
+        <v>0.0008461546009356224</v>
       </c>
       <c r="M11" t="n">
-        <v>102.5327717994904</v>
+        <v>102.290723549544</v>
       </c>
       <c r="N11" t="n">
-        <v>16339.73051695231</v>
+        <v>16290.17986558662</v>
       </c>
       <c r="O11" t="n">
-        <v>127.826955361349</v>
+        <v>127.632988939328</v>
       </c>
       <c r="P11" t="n">
-        <v>682.269352926044</v>
+        <v>681.6713101539191</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37922,7 +38078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80971,6 +81127,192 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-43.630566390400084,172.69585248014863</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-43.630535239617124,172.6948607896587</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-43.63059664162749,172.6938691051514</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-43.630641954116605,172.6928459837318</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-43.63036144119926,172.69184595060844</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>-43.63084036795272,172.69107190704023</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-43.63056098798363,172.6958524796844</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-43.63052956708008,172.69486078926448</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-43.63059646154696,172.69386910514183</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-43.63063998668557,172.6928463010476</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>-43.63035904880533,172.6918442239445</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>-43.63083901217899,172.69107092881023</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-43.63056467963488,172.6958524800016</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-43.63053442925469,172.69486078960233</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-43.63059871255359,172.69386910526126</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>-43.63064222240265,172.69284594046147</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>-43.63036080322756,172.69184549016472</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>-43.63084395676545,172.69107449647277</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L698"/>
+  <dimension ref="A1:L702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29740,6 +29740,174 @@
         <v>763.77</v>
       </c>
       <c r="L698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>650.4400000000001</v>
+      </c>
+      <c r="C699" t="n">
+        <v>661.95</v>
+      </c>
+      <c r="D699" t="n">
+        <v>208.23</v>
+      </c>
+      <c r="E699" t="n">
+        <v>204.88</v>
+      </c>
+      <c r="F699" t="n">
+        <v>212.66</v>
+      </c>
+      <c r="G699" t="n">
+        <v>225.59</v>
+      </c>
+      <c r="H699" t="n">
+        <v>182.93</v>
+      </c>
+      <c r="I699" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="J699" t="n">
+        <v>653.5</v>
+      </c>
+      <c r="K699" t="n">
+        <v>763.85</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:34+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>650.75</v>
+      </c>
+      <c r="C700" t="n">
+        <v>663.28</v>
+      </c>
+      <c r="D700" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="E700" t="n">
+        <v>203.51</v>
+      </c>
+      <c r="F700" t="n">
+        <v>212.01</v>
+      </c>
+      <c r="G700" t="n">
+        <v>224.72</v>
+      </c>
+      <c r="H700" t="n">
+        <v>182.39</v>
+      </c>
+      <c r="I700" t="n">
+        <v>200.76</v>
+      </c>
+      <c r="J700" t="n">
+        <v>655.0700000000001</v>
+      </c>
+      <c r="K700" t="n">
+        <v>764.17</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>650.1900000000001</v>
+      </c>
+      <c r="C701" t="n">
+        <v>663.13</v>
+      </c>
+      <c r="D701" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="E701" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="F701" t="n">
+        <v>211.46</v>
+      </c>
+      <c r="G701" t="n">
+        <v>224.48</v>
+      </c>
+      <c r="H701" t="n">
+        <v>181.89</v>
+      </c>
+      <c r="I701" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="J701" t="n">
+        <v>656.09</v>
+      </c>
+      <c r="K701" t="n">
+        <v>764.02</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>650.37</v>
+      </c>
+      <c r="C702" t="n">
+        <v>663.47</v>
+      </c>
+      <c r="D702" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="E702" t="n">
+        <v>202.75</v>
+      </c>
+      <c r="F702" t="n">
+        <v>210.94</v>
+      </c>
+      <c r="G702" t="n">
+        <v>224.86</v>
+      </c>
+      <c r="H702" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="I702" t="n">
+        <v>201.56</v>
+      </c>
+      <c r="J702" t="n">
+        <v>658.27</v>
+      </c>
+      <c r="K702" t="n">
+        <v>764.65</v>
+      </c>
+      <c r="L702" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29756,7 +29924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B745"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37209,6 +37377,46 @@
       </c>
       <c r="B745" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -37371,28 +37579,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03224105334600086</v>
+        <v>-0.02672471371330449</v>
       </c>
       <c r="J2" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K2" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002026508692181128</v>
+        <v>0.001403989358892632</v>
       </c>
       <c r="M2" t="n">
-        <v>4.589937339799802</v>
+        <v>4.592471477408345</v>
       </c>
       <c r="N2" t="n">
-        <v>29.42064027210501</v>
+        <v>29.39328267752442</v>
       </c>
       <c r="O2" t="n">
-        <v>5.424079670516004</v>
+        <v>5.421557218873967</v>
       </c>
       <c r="P2" t="n">
-        <v>646.2921994848366</v>
+        <v>646.2356786584345</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37443,28 +37651,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1265838148656299</v>
+        <v>-0.1205022314764026</v>
       </c>
       <c r="J3" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K3" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01806207140583116</v>
+        <v>0.01654206372943523</v>
       </c>
       <c r="M3" t="n">
-        <v>4.650775600747123</v>
+        <v>4.653076474780672</v>
       </c>
       <c r="N3" t="n">
-        <v>50.06520299455828</v>
+        <v>49.95192576767813</v>
       </c>
       <c r="O3" t="n">
-        <v>7.075676857697664</v>
+        <v>7.067667632796419</v>
       </c>
       <c r="P3" t="n">
-        <v>660.8130291628701</v>
+        <v>660.7507037092155</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37515,28 +37723,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5361965233959086</v>
+        <v>-0.5209540679121394</v>
       </c>
       <c r="J4" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K4" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0496074262642473</v>
+        <v>0.04736731240712</v>
       </c>
       <c r="M4" t="n">
-        <v>14.93742726316018</v>
+        <v>14.92751116561618</v>
       </c>
       <c r="N4" t="n">
-        <v>314.0376234369398</v>
+        <v>313.301885760003</v>
       </c>
       <c r="O4" t="n">
-        <v>17.72110672156058</v>
+        <v>17.70033575274783</v>
       </c>
       <c r="P4" t="n">
-        <v>207.2467880191672</v>
+        <v>207.0895787571249</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37587,28 +37795,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2984939824728031</v>
+        <v>-0.282870455505713</v>
       </c>
       <c r="J5" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K5" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03266637839605813</v>
+        <v>0.0295779184012771</v>
       </c>
       <c r="M5" t="n">
-        <v>10.8259318946732</v>
+        <v>10.84302192699004</v>
       </c>
       <c r="N5" t="n">
-        <v>151.6385405677398</v>
+        <v>151.9022479812939</v>
       </c>
       <c r="O5" t="n">
-        <v>12.31416016493775</v>
+        <v>12.32486300050812</v>
       </c>
       <c r="P5" t="n">
-        <v>197.3676325674301</v>
+        <v>197.2075601503797</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37659,28 +37867,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2190073414500813</v>
+        <v>0.2303397320110026</v>
       </c>
       <c r="J6" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K6" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01659351417635802</v>
+        <v>0.01848206651274631</v>
       </c>
       <c r="M6" t="n">
-        <v>10.5190392933298</v>
+        <v>10.50869512347212</v>
       </c>
       <c r="N6" t="n">
-        <v>163.4849589278122</v>
+        <v>163.1461738483959</v>
       </c>
       <c r="O6" t="n">
-        <v>12.78612368655224</v>
+        <v>12.77286866167487</v>
       </c>
       <c r="P6" t="n">
-        <v>195.6585784824971</v>
+        <v>195.5424667770941</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37731,28 +37939,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01257298090181849</v>
+        <v>-0.003524725901637454</v>
       </c>
       <c r="J7" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K7" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001882346328566653</v>
+        <v>1.486446733434121e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.954751943528786</v>
+        <v>5.967987779228336</v>
       </c>
       <c r="N7" t="n">
-        <v>48.29041991977452</v>
+        <v>48.39342519561207</v>
       </c>
       <c r="O7" t="n">
-        <v>6.949130875136438</v>
+        <v>6.95653830548011</v>
       </c>
       <c r="P7" t="n">
-        <v>217.0416480324473</v>
+        <v>216.9489339227066</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37803,28 +38011,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1180208311949069</v>
+        <v>0.1202069369045614</v>
       </c>
       <c r="J8" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K8" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004190611618922313</v>
+        <v>0.004400518017342869</v>
       </c>
       <c r="M8" t="n">
-        <v>11.22359497440162</v>
+        <v>11.16988861089533</v>
       </c>
       <c r="N8" t="n">
-        <v>189.3801635962178</v>
+        <v>188.3207511813215</v>
       </c>
       <c r="O8" t="n">
-        <v>13.76154655539187</v>
+        <v>13.72300080818046</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3583088618533</v>
+        <v>177.3358361157381</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37875,28 +38083,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.21525705032425</v>
+        <v>-0.2166030586043973</v>
       </c>
       <c r="J9" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K9" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04657320895587691</v>
+        <v>0.04768648803785991</v>
       </c>
       <c r="M9" t="n">
-        <v>5.755444014201252</v>
+        <v>5.729838298174744</v>
       </c>
       <c r="N9" t="n">
-        <v>54.27305948668909</v>
+        <v>53.97243787006206</v>
       </c>
       <c r="O9" t="n">
-        <v>7.367025144974672</v>
+        <v>7.346593623582432</v>
       </c>
       <c r="P9" t="n">
-        <v>208.0210041165188</v>
+        <v>208.0348431784923</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37947,28 +38155,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.539206624810384</v>
+        <v>2.502863401812773</v>
       </c>
       <c r="J10" t="n">
+        <v>701</v>
+      </c>
+      <c r="K10" t="n">
         <v>697</v>
       </c>
-      <c r="K10" t="n">
-        <v>693</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1328536701527865</v>
+        <v>0.1306967331523349</v>
       </c>
       <c r="M10" t="n">
-        <v>28.92341665401563</v>
+        <v>28.88210030134704</v>
       </c>
       <c r="N10" t="n">
-        <v>2400.305910898433</v>
+        <v>2392.574025595979</v>
       </c>
       <c r="O10" t="n">
-        <v>48.99291694621206</v>
+        <v>48.9139451035794</v>
       </c>
       <c r="P10" t="n">
-        <v>620.8902342170342</v>
+        <v>621.265194594213</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38019,28 +38227,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4899367842602421</v>
+        <v>0.5665326045778</v>
       </c>
       <c r="J11" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="K11" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0008461546009356224</v>
+        <v>0.001143362186886487</v>
       </c>
       <c r="M11" t="n">
-        <v>102.290723549544</v>
+        <v>101.9647183379924</v>
       </c>
       <c r="N11" t="n">
-        <v>16290.17986558662</v>
+        <v>16224.2679632422</v>
       </c>
       <c r="O11" t="n">
-        <v>127.632988939328</v>
+        <v>127.3745185005314</v>
       </c>
       <c r="P11" t="n">
-        <v>681.6713101539191</v>
+        <v>680.8864597011711</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38078,7 +38286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L698"/>
+  <dimension ref="A1:L702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81313,6 +81521,254 @@
         </is>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>-43.630558106694856,172.69585247943678</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>-43.630527946355215,172.69486078915185</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>-43.63059799223148,172.69386910522303</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>-43.63063936068478,172.69284640201175</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>-43.63035657666494,172.69184243972526</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>-43.63083925143317,172.69107110143906</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:34+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-43.63054343013011,172.69585247817562</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>-43.630515610838145,172.69486078829462</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>-43.63059213961424,172.69386910491258</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>-43.63063158038931,172.69284765685137</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>-43.63035227035578,172.69183933173082</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>-43.63083334982982,172.69106684326192</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>-43.63053694723035,172.6958524776185</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-43.630513359831376,172.6948607881382</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>-43.630587187399655,172.6938691046499</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>-43.63062943410091,172.69284800301395</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>-43.63034828303241,172.69183645395856</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>-43.63083127629348,172.69106534714584</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>-43.63053892811638,172.69585247778872</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-43.63050876777757,172.69486078781907</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>-43.63058250530585,172.69386910440156</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>-43.630632832390894,172.69284745492317</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>-43.6303545830033,172.6918410008389</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>-43.630839729941556,172.6910714466967</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L702"/>
+  <dimension ref="A1:L705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29908,6 +29908,132 @@
         <v>764.65</v>
       </c>
       <c r="L702" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>648.72</v>
+      </c>
+      <c r="C703" t="n">
+        <v>660.91</v>
+      </c>
+      <c r="D703" t="n">
+        <v>203.65</v>
+      </c>
+      <c r="E703" t="n">
+        <v>202.65</v>
+      </c>
+      <c r="F703" t="n">
+        <v>211.03</v>
+      </c>
+      <c r="G703" t="n">
+        <v>224.35</v>
+      </c>
+      <c r="H703" t="n">
+        <v>179.64</v>
+      </c>
+      <c r="I703" t="n">
+        <v>202.51</v>
+      </c>
+      <c r="J703" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="K703" t="n">
+        <v>766.36</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>648.5700000000001</v>
+      </c>
+      <c r="C704" t="n">
+        <v>662.37</v>
+      </c>
+      <c r="D704" t="n">
+        <v>200.74</v>
+      </c>
+      <c r="E704" t="n">
+        <v>198.51</v>
+      </c>
+      <c r="F704" t="n">
+        <v>209.02</v>
+      </c>
+      <c r="G704" t="n">
+        <v>222.49</v>
+      </c>
+      <c r="H704" t="n">
+        <v>179.39</v>
+      </c>
+      <c r="I704" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="J704" t="n">
+        <v>658.66</v>
+      </c>
+      <c r="K704" t="n">
+        <v>767.64</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>647.52</v>
+      </c>
+      <c r="C705" t="n">
+        <v>661.53</v>
+      </c>
+      <c r="D705" t="n">
+        <v>198.81</v>
+      </c>
+      <c r="E705" t="n">
+        <v>196.43</v>
+      </c>
+      <c r="F705" t="n">
+        <v>207.39</v>
+      </c>
+      <c r="G705" t="n">
+        <v>221.7</v>
+      </c>
+      <c r="H705" t="n">
+        <v>178.55</v>
+      </c>
+      <c r="I705" t="n">
+        <v>199.77</v>
+      </c>
+      <c r="J705" t="n">
+        <v>661.26</v>
+      </c>
+      <c r="K705" t="n">
+        <v>767.9</v>
+      </c>
+      <c r="L705" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29924,7 +30050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B749"/>
+  <dimension ref="A1:B752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37417,6 +37543,36 @@
       </c>
       <c r="B749" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -37579,28 +37735,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02672471371330449</v>
+        <v>-0.02446550976884547</v>
       </c>
       <c r="J2" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001403989358892632</v>
+        <v>0.001186611776921587</v>
       </c>
       <c r="M2" t="n">
-        <v>4.592471477408345</v>
+        <v>4.584612122726674</v>
       </c>
       <c r="N2" t="n">
-        <v>29.39328267752442</v>
+        <v>29.30090736884348</v>
       </c>
       <c r="O2" t="n">
-        <v>5.421557218873967</v>
+        <v>5.413031255114225</v>
       </c>
       <c r="P2" t="n">
-        <v>646.2356786584345</v>
+        <v>646.2124249294036</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37651,28 +37807,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1205022314764026</v>
+        <v>-0.1171500951819282</v>
       </c>
       <c r="J3" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K3" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01654206372943523</v>
+        <v>0.01577101372265854</v>
       </c>
       <c r="M3" t="n">
-        <v>4.653076474780672</v>
+        <v>4.649084711022751</v>
       </c>
       <c r="N3" t="n">
-        <v>49.95192576767813</v>
+        <v>49.81024333560404</v>
       </c>
       <c r="O3" t="n">
-        <v>7.067667632796419</v>
+        <v>7.057637234627751</v>
       </c>
       <c r="P3" t="n">
-        <v>660.7507037092155</v>
+        <v>660.7161905346608</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37723,28 +37879,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5209540679121394</v>
+        <v>-0.514408517865011</v>
       </c>
       <c r="J4" t="n">
+        <v>704</v>
+      </c>
+      <c r="K4" t="n">
         <v>701</v>
       </c>
-      <c r="K4" t="n">
-        <v>698</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04736731240712</v>
+        <v>0.0466143107618443</v>
       </c>
       <c r="M4" t="n">
-        <v>14.92751116561618</v>
+        <v>14.89569174877328</v>
       </c>
       <c r="N4" t="n">
-        <v>313.301885760003</v>
+        <v>312.2406528228097</v>
       </c>
       <c r="O4" t="n">
-        <v>17.70033575274783</v>
+        <v>17.67033256118316</v>
       </c>
       <c r="P4" t="n">
-        <v>207.0895787571249</v>
+        <v>207.0217623161999</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37795,28 +37951,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.282870455505713</v>
+        <v>-0.275014250597821</v>
       </c>
       <c r="J5" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K5" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0295779184012771</v>
+        <v>0.0281839609320107</v>
       </c>
       <c r="M5" t="n">
-        <v>10.84302192699004</v>
+        <v>10.83631094214291</v>
       </c>
       <c r="N5" t="n">
-        <v>151.9022479812939</v>
+        <v>151.6663592451666</v>
       </c>
       <c r="O5" t="n">
-        <v>12.32486300050812</v>
+        <v>12.31528965331984</v>
       </c>
       <c r="P5" t="n">
-        <v>197.2075601503797</v>
+        <v>197.1267038316406</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37867,28 +38023,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2303397320110026</v>
+        <v>0.2364752572799911</v>
       </c>
       <c r="J6" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01848206651274631</v>
+        <v>0.01961043129832829</v>
       </c>
       <c r="M6" t="n">
-        <v>10.50869512347212</v>
+        <v>10.49091076483261</v>
       </c>
       <c r="N6" t="n">
-        <v>163.1461738483959</v>
+        <v>162.6934305799361</v>
       </c>
       <c r="O6" t="n">
-        <v>12.77286866167487</v>
+        <v>12.75513349910287</v>
       </c>
       <c r="P6" t="n">
-        <v>195.5424667770941</v>
+        <v>195.4793103112486</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37939,28 +38095,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003524725901637454</v>
+        <v>0.001406084930719681</v>
       </c>
       <c r="J7" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K7" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L7" t="n">
-        <v>1.486446733434121e-05</v>
+        <v>2.379982194877783e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>5.967987779228336</v>
+        <v>5.968312422990369</v>
       </c>
       <c r="N7" t="n">
-        <v>48.39342519561207</v>
+        <v>48.34320431202466</v>
       </c>
       <c r="O7" t="n">
-        <v>6.95653830548011</v>
+        <v>6.952927751100587</v>
       </c>
       <c r="P7" t="n">
-        <v>216.9489339227066</v>
+        <v>216.8981766776795</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38011,28 +38167,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1202069369045614</v>
+        <v>0.1190878004454332</v>
       </c>
       <c r="J8" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K8" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004400518017342869</v>
+        <v>0.004359539920349209</v>
       </c>
       <c r="M8" t="n">
-        <v>11.16988861089533</v>
+        <v>11.12835036158783</v>
       </c>
       <c r="N8" t="n">
-        <v>188.3207511813215</v>
+        <v>187.5257428582238</v>
       </c>
       <c r="O8" t="n">
-        <v>13.72300080818046</v>
+        <v>13.69400390164337</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3358361157381</v>
+        <v>177.3474020256078</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38083,28 +38239,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2166030586043973</v>
+        <v>-0.217839540784306</v>
       </c>
       <c r="J9" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K9" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04768648803785991</v>
+        <v>0.04862354370390087</v>
       </c>
       <c r="M9" t="n">
-        <v>5.729838298174744</v>
+        <v>5.712771452143943</v>
       </c>
       <c r="N9" t="n">
-        <v>53.97243787006206</v>
+        <v>53.75807228397801</v>
       </c>
       <c r="O9" t="n">
-        <v>7.346593623582432</v>
+        <v>7.331989653837354</v>
       </c>
       <c r="P9" t="n">
-        <v>208.0348431784923</v>
+        <v>208.0476272316018</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38155,28 +38311,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.502863401812773</v>
+        <v>2.478565853146616</v>
       </c>
       <c r="J10" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K10" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1306967331523349</v>
+        <v>0.1293761592162611</v>
       </c>
       <c r="M10" t="n">
-        <v>28.88210030134704</v>
+        <v>28.84080954803705</v>
       </c>
       <c r="N10" t="n">
-        <v>2392.574025595979</v>
+        <v>2385.957844893253</v>
       </c>
       <c r="O10" t="n">
-        <v>48.9139451035794</v>
+        <v>48.84626746122218</v>
       </c>
       <c r="P10" t="n">
-        <v>621.265194594213</v>
+        <v>621.5170693671108</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38227,28 +38383,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5665326045778</v>
+        <v>0.6252320598398713</v>
       </c>
       <c r="J11" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K11" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001143362186886487</v>
+        <v>0.001403411678069788</v>
       </c>
       <c r="M11" t="n">
-        <v>101.9647183379924</v>
+        <v>101.7263317483714</v>
       </c>
       <c r="N11" t="n">
-        <v>16224.2679632422</v>
+        <v>16176.49025184742</v>
       </c>
       <c r="O11" t="n">
-        <v>127.3745185005314</v>
+        <v>127.1868320693908</v>
       </c>
       <c r="P11" t="n">
-        <v>680.8864597011711</v>
+        <v>680.2821227040029</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38286,7 +38442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L702"/>
+  <dimension ref="A1:L705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81769,6 +81925,192 @@
         </is>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>-43.63051686824905,172.69585247589305</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-43.63050786737485,172.6948607877565</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>-43.63058331566825,172.69386910444453</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>-43.630628271528025,172.6928481905187</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>-43.630330340076306,172.69182350398808</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>-43.630847306323986,172.69107691327676</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>-43.630490666528985,172.69585247364137</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-43.630470590702615,172.69486078516593</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>-43.63056521757488,172.6938691034845</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>-43.630611637792775,172.69285087327785</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>-43.63032834641444,172.69182206510294</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>-43.6308272089721,172.69106241245686</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-43.6304732887558,172.69585247214792</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-43.63045186232611,172.69486078386436</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>-43.63055054101158,172.69386910270597</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>-43.63060457292669,172.69285201272885</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>-43.63032164771037,172.6918172304496</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>-43.6308254544413,172.69106114651274</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L705"/>
+  <dimension ref="A1:L707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30034,6 +30034,90 @@
         <v>767.9</v>
       </c>
       <c r="L705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>645.7</v>
+      </c>
+      <c r="C706" t="n">
+        <v>660</v>
+      </c>
+      <c r="D706" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="E706" t="n">
+        <v>195.12</v>
+      </c>
+      <c r="F706" t="n">
+        <v>206.66</v>
+      </c>
+      <c r="G706" t="n">
+        <v>218.99</v>
+      </c>
+      <c r="H706" t="n">
+        <v>177.76</v>
+      </c>
+      <c r="I706" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="J706" t="n">
+        <v>661.21</v>
+      </c>
+      <c r="K706" t="n">
+        <v>727.84</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>644.75</v>
+      </c>
+      <c r="C707" t="n">
+        <v>659.66</v>
+      </c>
+      <c r="D707" t="n">
+        <v>192.02</v>
+      </c>
+      <c r="E707" t="n">
+        <v>192.41</v>
+      </c>
+      <c r="F707" t="n">
+        <v>206.66</v>
+      </c>
+      <c r="G707" t="n">
+        <v>217.31</v>
+      </c>
+      <c r="H707" t="n">
+        <v>175.65</v>
+      </c>
+      <c r="I707" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="J707" t="n">
+        <v>669.3</v>
+      </c>
+      <c r="K707" t="n">
+        <v>693.09</v>
+      </c>
+      <c r="L707" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30050,7 +30134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B752"/>
+  <dimension ref="A1:B754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37573,6 +37657,26 @@
       </c>
       <c r="B752" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -37735,28 +37839,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02446550976884547</v>
+        <v>-0.02464732560494132</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K2" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001186611776921587</v>
+        <v>0.001211773682022299</v>
       </c>
       <c r="M2" t="n">
-        <v>4.584612122726674</v>
+        <v>4.572975793130293</v>
       </c>
       <c r="N2" t="n">
-        <v>29.30090736884348</v>
+        <v>29.21885602497549</v>
       </c>
       <c r="O2" t="n">
-        <v>5.413031255114225</v>
+        <v>5.405446884853785</v>
       </c>
       <c r="P2" t="n">
-        <v>646.2124249294036</v>
+        <v>646.2143054739793</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37807,28 +37911,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1171500951819282</v>
+        <v>-0.115914649062423</v>
       </c>
       <c r="J3" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K3" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01577101372265854</v>
+        <v>0.01553589779330011</v>
       </c>
       <c r="M3" t="n">
-        <v>4.649084711022751</v>
+        <v>4.641739281779324</v>
       </c>
       <c r="N3" t="n">
-        <v>49.81024333560404</v>
+        <v>49.68346583578778</v>
       </c>
       <c r="O3" t="n">
-        <v>7.057637234627751</v>
+        <v>7.048649930007007</v>
       </c>
       <c r="P3" t="n">
-        <v>660.7161905346608</v>
+        <v>660.7034203609885</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37879,28 +37983,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.514408517865011</v>
+        <v>-0.5144681838269389</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K4" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0466143107618443</v>
+        <v>0.04690288701139389</v>
       </c>
       <c r="M4" t="n">
-        <v>14.89569174877328</v>
+        <v>14.85647666630881</v>
       </c>
       <c r="N4" t="n">
-        <v>312.2406528228097</v>
+        <v>311.3558571778655</v>
       </c>
       <c r="O4" t="n">
-        <v>17.67033256118316</v>
+        <v>17.64527860867789</v>
       </c>
       <c r="P4" t="n">
-        <v>207.0217623161999</v>
+        <v>207.0223858424321</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37951,28 +38055,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.275014250597821</v>
+        <v>-0.272816966389095</v>
       </c>
       <c r="J5" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K5" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0281839609320107</v>
+        <v>0.0279074726995383</v>
       </c>
       <c r="M5" t="n">
-        <v>10.83631094214291</v>
+        <v>10.81658792565433</v>
       </c>
       <c r="N5" t="n">
-        <v>151.6663592451666</v>
+        <v>151.2869795846251</v>
       </c>
       <c r="O5" t="n">
-        <v>12.31528965331984</v>
+        <v>12.29987721827438</v>
       </c>
       <c r="P5" t="n">
-        <v>197.1267038316406</v>
+        <v>197.1039941589441</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38023,28 +38127,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2364752572799911</v>
+        <v>0.2391316582221036</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K6" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01961043129832829</v>
+        <v>0.02015929581485987</v>
       </c>
       <c r="M6" t="n">
-        <v>10.49091076483261</v>
+        <v>10.47285240331389</v>
       </c>
       <c r="N6" t="n">
-        <v>162.6934305799361</v>
+        <v>162.2978338872244</v>
       </c>
       <c r="O6" t="n">
-        <v>12.75513349910287</v>
+        <v>12.73961670880346</v>
       </c>
       <c r="P6" t="n">
-        <v>195.4793103112486</v>
+        <v>195.4518492516771</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38095,28 +38199,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001406084930719681</v>
+        <v>0.002071249702023264</v>
       </c>
       <c r="J7" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K7" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L7" t="n">
-        <v>2.379982194877783e-06</v>
+        <v>5.195942018310085e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>5.968312422990369</v>
+        <v>5.954828369218422</v>
       </c>
       <c r="N7" t="n">
-        <v>48.34320431202466</v>
+        <v>48.21218549123702</v>
       </c>
       <c r="O7" t="n">
-        <v>6.952927751100587</v>
+        <v>6.943499513302857</v>
       </c>
       <c r="P7" t="n">
-        <v>216.8981766776795</v>
+        <v>216.8913024209824</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38167,28 +38271,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1190878004454332</v>
+        <v>0.1169771882663382</v>
       </c>
       <c r="J8" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K8" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004359539920349209</v>
+        <v>0.00423226693715173</v>
       </c>
       <c r="M8" t="n">
-        <v>11.12835036158783</v>
+        <v>11.10822024237229</v>
       </c>
       <c r="N8" t="n">
-        <v>187.5257428582238</v>
+        <v>187.0381902858946</v>
       </c>
       <c r="O8" t="n">
-        <v>13.69400390164337</v>
+        <v>13.67619063503776</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3474020256078</v>
+        <v>177.3692951273795</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38239,28 +38343,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.217839540784306</v>
+        <v>-0.2197534529603881</v>
       </c>
       <c r="J9" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K9" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04862354370390087</v>
+        <v>0.04970366285123418</v>
       </c>
       <c r="M9" t="n">
-        <v>5.712771452143943</v>
+        <v>5.706813490729895</v>
       </c>
       <c r="N9" t="n">
-        <v>53.75807228397801</v>
+        <v>53.63953620041036</v>
       </c>
       <c r="O9" t="n">
-        <v>7.331989653837354</v>
+        <v>7.323901706086065</v>
       </c>
       <c r="P9" t="n">
-        <v>208.0476272316018</v>
+        <v>208.0674776833432</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38311,28 +38415,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.478565853146616</v>
+        <v>2.466025420301135</v>
       </c>
       <c r="J10" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K10" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1293761592162611</v>
+        <v>0.1288673153780757</v>
       </c>
       <c r="M10" t="n">
-        <v>28.84080954803705</v>
+        <v>28.80090321745245</v>
       </c>
       <c r="N10" t="n">
-        <v>2385.957844893253</v>
+        <v>2380.659442263828</v>
       </c>
       <c r="O10" t="n">
-        <v>48.84626746122218</v>
+        <v>48.79200182677308</v>
       </c>
       <c r="P10" t="n">
-        <v>621.5170693671108</v>
+        <v>621.6475889442395</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38383,28 +38487,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6252320598398713</v>
+        <v>0.6325857841146957</v>
       </c>
       <c r="J11" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K11" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001403411678069788</v>
+        <v>0.00144541799212039</v>
       </c>
       <c r="M11" t="n">
-        <v>101.7263317483714</v>
+        <v>101.4741652734084</v>
       </c>
       <c r="N11" t="n">
-        <v>16176.49025184742</v>
+        <v>16132.02601700267</v>
       </c>
       <c r="O11" t="n">
-        <v>127.1868320693908</v>
+        <v>127.0119128940379</v>
       </c>
       <c r="P11" t="n">
-        <v>680.2821227040029</v>
+        <v>680.206150369195</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38442,7 +38546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L705"/>
+  <dimension ref="A1:L707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82111,6 +82215,130 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>-43.63043214034967,172.6958524686116</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-43.630440067050515,172.6948607830446</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>-43.63054396807216,172.69386910235727</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>-43.63058033775301,172.69285592147648</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-43.63031534773852,172.6918126835742</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>-43.63081716029546,172.69105516205056</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>-43.63041215140829,172.69585246689368</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>-43.63041566613676,172.6948607813487</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>-43.63054396807216,172.69386910235727</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>-43.63056531373379,172.69285834460993</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>-43.63029852123048,172.69180053939266</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>-43.63081716029546,172.69105516205056</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
